--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-05T14:49:09.919Z</t>
+    <t>2026-09-06T07:32:46.095Z</t>
   </si>
   <si>
     <t>Car, MultiCar and MultiCover Insurance Quotes – Admiral</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero-trust","cards-product","video-advert","columns-notice","cards-article","columns-award","carousel-review","columns-app","columns-links"]</t>
+    <t>["hero-trust","cards-product","video-advert","columns-notice","cards-article","columns-award","carousel-review","app-download","columns-links"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-06T07:32:46.095Z</t>
+    <t>2026-09-06T11:21:56.282Z</t>
   </si>
   <si>
     <t>Car, MultiCar and MultiCover Insurance Quotes – Admiral</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero-trust","cards-product","video-advert","columns-notice","cards-article","columns-award","carousel-review","app-download","columns-links"]</t>
+    <t>["hero-trust","cards-product","video-advert","columns-notice","cards-article","award-banner","carousel-review","app-download","columns-links"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-06T11:21:56.282Z</t>
+    <t>2026-09-07T09:16:56.298Z</t>
   </si>
   <si>
     <t>Car, MultiCar and MultiCover Insurance Quotes – Admiral</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-07T09:16:56.298Z</t>
+    <t>2026-09-07T09:38:12.441Z</t>
   </si>
   <si>
     <t>Car, MultiCar and MultiCover Insurance Quotes – Admiral</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero-trust","cards-product","video-advert","columns-notice","cards-article","award-banner","carousel-review","app-download","columns-links"]</t>
+    <t>["hero-trust","cards-product","video-advert","notice-banner","cards-article","award-banner","carousel-review","app-download","columns-links"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-07T09:38:12.441Z</t>
+    <t>2026-09-07T10:00:56.671Z</t>
   </si>
   <si>
     <t>Car, MultiCar and MultiCover Insurance Quotes – Admiral</t>
